--- a/artfynd/A 12419-2023 artfynd.xlsx
+++ b/artfynd/A 12419-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122661372</v>
       </c>
       <c r="B2" t="n">
-        <v>57300</v>
+        <v>57394</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 12419-2023 artfynd.xlsx
+++ b/artfynd/A 12419-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -803,6 +803,134 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>126010623</v>
+      </c>
+      <c r="B3" t="n">
+        <v>57588</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>100082</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Röd glada</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Milvus milvus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>SV Stora Myggtäppan, Srm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>597537</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6542929</v>
+      </c>
+      <c r="S3" t="n">
+        <v>50</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Flen</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Forssa</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>10:42</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>10:42</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Flyger västerut, sannolikt samma individ som sågs vid Malstagård 10:15.</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Tomas Carlberg</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Tomas Carlberg</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 12419-2023 artfynd.xlsx
+++ b/artfynd/A 12419-2023 artfynd.xlsx
@@ -809,7 +809,7 @@
         <v>126010623</v>
       </c>
       <c r="B3" t="n">
-        <v>57588</v>
+        <v>57589</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 12419-2023 artfynd.xlsx
+++ b/artfynd/A 12419-2023 artfynd.xlsx
@@ -809,7 +809,7 @@
         <v>126010623</v>
       </c>
       <c r="B3" t="n">
-        <v>57589</v>
+        <v>57593</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 12419-2023 artfynd.xlsx
+++ b/artfynd/A 12419-2023 artfynd.xlsx
@@ -809,7 +809,7 @@
         <v>126010623</v>
       </c>
       <c r="B3" t="n">
-        <v>57593</v>
+        <v>57594</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 12419-2023 artfynd.xlsx
+++ b/artfynd/A 12419-2023 artfynd.xlsx
@@ -937,7 +937,7 @@
         <v>126990849</v>
       </c>
       <c r="B4" t="n">
-        <v>101622</v>
+        <v>101697</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
         <v>126994681</v>
       </c>
       <c r="B5" t="n">
-        <v>109185</v>
+        <v>109260</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 12419-2023 artfynd.xlsx
+++ b/artfynd/A 12419-2023 artfynd.xlsx
@@ -937,7 +937,7 @@
         <v>126990849</v>
       </c>
       <c r="B4" t="n">
-        <v>101697</v>
+        <v>101703</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
         <v>126994681</v>
       </c>
       <c r="B5" t="n">
-        <v>109260</v>
+        <v>109266</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 12419-2023 artfynd.xlsx
+++ b/artfynd/A 12419-2023 artfynd.xlsx
@@ -937,7 +937,7 @@
         <v>126990849</v>
       </c>
       <c r="B4" t="n">
-        <v>101703</v>
+        <v>101704</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
         <v>126994681</v>
       </c>
       <c r="B5" t="n">
-        <v>109266</v>
+        <v>109267</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 12419-2023 artfynd.xlsx
+++ b/artfynd/A 12419-2023 artfynd.xlsx
@@ -937,7 +937,7 @@
         <v>126990849</v>
       </c>
       <c r="B4" t="n">
-        <v>101704</v>
+        <v>101708</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
         <v>126994681</v>
       </c>
       <c r="B5" t="n">
-        <v>109267</v>
+        <v>109273</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 12419-2023 artfynd.xlsx
+++ b/artfynd/A 12419-2023 artfynd.xlsx
@@ -937,7 +937,7 @@
         <v>126990849</v>
       </c>
       <c r="B4" t="n">
-        <v>101708</v>
+        <v>101709</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
         <v>126994681</v>
       </c>
       <c r="B5" t="n">
-        <v>109273</v>
+        <v>109275</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 12419-2023 artfynd.xlsx
+++ b/artfynd/A 12419-2023 artfynd.xlsx
@@ -937,7 +937,7 @@
         <v>126990849</v>
       </c>
       <c r="B4" t="n">
-        <v>101709</v>
+        <v>101711</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
         <v>126994681</v>
       </c>
       <c r="B5" t="n">
-        <v>109275</v>
+        <v>109277</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 12419-2023 artfynd.xlsx
+++ b/artfynd/A 12419-2023 artfynd.xlsx
@@ -809,7 +809,7 @@
         <v>126010623</v>
       </c>
       <c r="B3" t="n">
-        <v>57594</v>
+        <v>57763</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -937,7 +937,7 @@
         <v>126990849</v>
       </c>
       <c r="B4" t="n">
-        <v>101711</v>
+        <v>101697</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
         <v>126994681</v>
       </c>
       <c r="B5" t="n">
-        <v>109277</v>
+        <v>109260</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 12419-2023 artfynd.xlsx
+++ b/artfynd/A 12419-2023 artfynd.xlsx
@@ -809,7 +809,7 @@
         <v>126010623</v>
       </c>
       <c r="B3" t="n">
-        <v>57763</v>
+        <v>57789</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 12419-2023 artfynd.xlsx
+++ b/artfynd/A 12419-2023 artfynd.xlsx
@@ -809,7 +809,7 @@
         <v>126010623</v>
       </c>
       <c r="B3" t="n">
-        <v>57789</v>
+        <v>57791</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 12419-2023 artfynd.xlsx
+++ b/artfynd/A 12419-2023 artfynd.xlsx
@@ -809,7 +809,7 @@
         <v>126010623</v>
       </c>
       <c r="B3" t="n">
-        <v>57791</v>
+        <v>57799</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 12419-2023 artfynd.xlsx
+++ b/artfynd/A 12419-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122661372</v>
+        <v>96381</v>
       </c>
       <c r="B2" t="n">
-        <v>57394</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92205</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,51 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100067</v>
+        <v>73</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Havsörn</t>
+          <t>Veckticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Haliaeetus albicilla</t>
+          <t>Fomitopsis pulvinascens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>5K+</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
+          <t>(Pilát) Niemelä &amp; Miettinen</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Stora Myggtäppan, Stora Myggtäppan, Srm</t>
+          <t>SO NYSTUGAN (09H8a01), Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>597470</v>
+        <v>597323</v>
       </c>
       <c r="R2" t="n">
-        <v>6543099</v>
+        <v>6543197</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -759,27 +740,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-02-18</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>11:06</t>
+          <t>1995-05-19</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-02-18</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>11:06</t>
+          <t>1995-05-19</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Kretsar lugnt över området</t>
+          <t>090780011 / ANT PULV / Enstaka-sparsam (1)  / OBJ.AREA:0,4 ha</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,80 +761,94 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>Lövskogslund /</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Låga av asp</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Thomas Strid</t>
+          <t>Niklas Lönnell</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Thomas Strid</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+          <t>Bo Westman</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126010623</v>
+        <v>126988043</v>
       </c>
       <c r="B3" t="n">
-        <v>57799</v>
+        <v>107708</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100082</v>
+        <v>245</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Röd glada</t>
+          <t>Skogsklocka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Milvus milvus</t>
+          <t>Campanula cervicaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>adult</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>SV Stora Myggtäppan, Srm</t>
+          <t>Asplunda OSO om, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>597537</v>
+        <v>597378</v>
       </c>
       <c r="R3" t="n">
-        <v>6542929</v>
+        <v>6542965</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -887,27 +872,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>10:42</t>
+          <t>2025-07-28</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>10:42</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Flyger västerut, sannolikt samma individ som sågs vid Malstagård 10:15.</t>
+          <t>2025-07-28</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -916,28 +886,34 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Skogsbryn mot åkermark</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Tomas Carlberg</t>
+          <t>Rolf Olsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Tomas Carlberg</t>
+          <t>Rolf Olsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126990849</v>
+        <v>129465</v>
       </c>
       <c r="B4" t="n">
-        <v>101711</v>
+        <v>92699</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -945,41 +921,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221317</v>
+        <v>366</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gullklöver</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Trifolium aureum</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Pollich</t>
+          <t>(Pers.) Jülich</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Forsagården NV om, Srm</t>
+          <t>SO NYSTUGAN (09H8a01), Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>597502</v>
+        <v>597323</v>
       </c>
       <c r="R4" t="n">
-        <v>6542951</v>
+        <v>6543197</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1003,12 +975,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-07-28</t>
+          <t>1995-05-19</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-07-28</t>
+          <t>1995-05-19</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>090780011 / CLA PYXI / Enstaka-sparsam (1)  / OBJ.AREA:0,4 ha</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1017,76 +994,80 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Vägren grusväg</t>
+          <t>Lövskogslund /</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Låga av asp</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Rolf Olsson</t>
+          <t>Niklas Lönnell</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Rolf Olsson</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
+          <t>Bo Westman</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126994681</v>
+        <v>1497496</v>
       </c>
       <c r="B5" t="n">
-        <v>109277</v>
+        <v>91966</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220299</v>
+        <v>5321</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Asplunda OSO om, Srm</t>
+          <t>SO NYSTUGAN (09H8a01), Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>597437</v>
+        <v>597323</v>
       </c>
       <c r="R5" t="n">
-        <v>6542974</v>
+        <v>6543197</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1110,12 +1091,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-07-28</t>
+          <t>1995-05-19</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-07-28</t>
+          <t>1995-05-19</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>090780011 / OXY CORT / Enstaka-sparsam (1)  / OBJ.AREA:0,4 ha</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1124,27 +1110,830 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Skogsbryn</t>
+          <t>Lövskogslund /</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Låga av asp</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
+          <t>Niklas Lönnell</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Bo Westman</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>122661372</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57899</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100067</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Havsörn</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Haliaeetus albicilla</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>5K+</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Stora Myggtäppan, Stora Myggtäppan, Srm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>597470</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6543099</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Flen</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Forssa</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-02-18</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>11:06</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-02-18</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>11:06</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Kretsar lugnt över området</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Thomas Strid</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Thomas Strid</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>126010623</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57890</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100082</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Röd glada</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Milvus milvus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>SV Stora Myggtäppan, Srm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>597537</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6542929</v>
+      </c>
+      <c r="S7" t="n">
+        <v>50</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Flen</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Forssa</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>10:42</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>10:42</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Flyger västerut, sannolikt samma individ som sågs vid Malstagård 10:15.</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Tomas Carlberg</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Tomas Carlberg</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>126010551</v>
+      </c>
+      <c r="B8" t="n">
+        <v>58676</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>103055</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Gulsparv</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Emberiza citrinella</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Ö Asplunda, Srm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>597335</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6543009</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Flen</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Forssa</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Tomas Carlberg</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Tomas Carlberg</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>126994787</v>
+      </c>
+      <c r="B9" t="n">
+        <v>111399</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>219716</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Krusfrö</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Selinum carvifolia</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Forsagården NNV om, Srm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>597615</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6542907</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Flen</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Forssa</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Frisk gräsmark</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
           <t>Rolf Olsson</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
+      <c r="AX9" t="inlineStr">
         <is>
           <t>Rolf Olsson</t>
         </is>
       </c>
-      <c r="AY5" t="inlineStr"/>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>126988836</v>
+      </c>
+      <c r="B10" t="n">
+        <v>110078</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Forsagården NNV om, Srm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>597557</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6542910</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Flen</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Forssa</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Skogsbryn mot åkermark</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>126994681</v>
+      </c>
+      <c r="B11" t="n">
+        <v>110078</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Asplunda OSO om, Srm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>597437</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6542974</v>
+      </c>
+      <c r="S11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Flen</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Forssa</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Skogsbryn</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>126990849</v>
+      </c>
+      <c r="B12" t="n">
+        <v>102419</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>221317</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Gullklöver</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Trifolium aureum</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Pollich</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Forsagården NV om, Srm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>597502</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6542951</v>
+      </c>
+      <c r="S12" t="n">
+        <v>25</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Flen</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Forssa</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>Vägren grusväg</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 12419-2023 artfynd.xlsx
+++ b/artfynd/A 12419-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AZ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -788,6 +793,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96381</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -907,6 +917,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126988043</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1023,6 +1038,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129465</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1139,6 +1159,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1497496</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1265,6 +1290,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122661372</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1393,6 +1423,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126010623</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1506,6 +1541,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126010551</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1613,6 +1653,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126994787</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1720,6 +1765,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126988836</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1827,6 +1877,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126994681</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1934,8 +1989,26 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126990849</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>